--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1895.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1895.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645A4775-945C-4CA3-BBD1-0F47EC833CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841BC1FC-B516-44CA-83D7-C65E7CE26F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Notes" sheetId="2" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="303">
   <si>
     <t>губ</t>
   </si>
@@ -939,6 +940,9 @@
   </si>
   <si>
     <t>[Астраханская (сумма)]</t>
+  </si>
+  <si>
+    <t>Петербург без пригородов</t>
   </si>
 </sst>
 </file>
@@ -1200,11 +1204,11 @@
     <xf numFmtId="3" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1371,6 +1375,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1874904B-D71C-4790-8B63-1651C1F38481}">
+  <dimension ref="A2"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AM282"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1428,23 +1447,23 @@
         <v>284</v>
       </c>
       <c r="J1" s="3"/>
-      <c r="K1" s="50" t="s">
+      <c r="K1" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
-      <c r="S1" s="50"/>
-      <c r="T1" s="50"/>
-      <c r="U1" s="50"/>
-      <c r="V1" s="50"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="50"/>
-      <c r="Y1" s="50"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="51"/>
+      <c r="V1" s="51"/>
+      <c r="W1" s="51"/>
+      <c r="X1" s="51"/>
+      <c r="Y1" s="51"/>
       <c r="AA1" s="36" t="s">
         <v>285</v>
       </c>
@@ -6387,7 +6406,7 @@
       <c r="K75" s="8">
         <v>101703</v>
       </c>
-      <c r="L75" s="51">
+      <c r="L75" s="50">
         <v>67589</v>
       </c>
       <c r="M75" s="8">
@@ -9019,7 +9038,7 @@
       <c r="R112" s="8">
         <v>206811</v>
       </c>
-      <c r="S112" s="51">
+      <c r="S112" s="50">
         <v>183627</v>
       </c>
       <c r="T112" s="8">
@@ -9415,7 +9434,7 @@
       <c r="Q117" s="5">
         <v>4240</v>
       </c>
-      <c r="R117" s="51">
+      <c r="R117" s="50">
         <v>4824</v>
       </c>
       <c r="S117" s="5">
@@ -9556,7 +9575,7 @@
       <c r="Q119" s="8">
         <v>120384</v>
       </c>
-      <c r="R119" s="51">
+      <c r="R119" s="50">
         <v>207611</v>
       </c>
       <c r="S119" s="8">
@@ -9565,7 +9584,7 @@
       <c r="T119" s="8">
         <v>112222</v>
       </c>
-      <c r="U119" s="51">
+      <c r="U119" s="50">
         <v>178352</v>
       </c>
       <c r="V119" s="8"/>
@@ -10855,7 +10874,7 @@
       <c r="V137" s="8">
         <v>184123</v>
       </c>
-      <c r="W137" s="51">
+      <c r="W137" s="50">
         <v>231455</v>
       </c>
       <c r="X137" s="8">
@@ -11488,7 +11507,7 @@
       <c r="L146" s="8">
         <v>303234</v>
       </c>
-      <c r="M146" s="51">
+      <c r="M146" s="50">
         <v>406235</v>
       </c>
       <c r="N146" s="8">
@@ -12812,7 +12831,7 @@
       <c r="T165" s="8">
         <v>164985</v>
       </c>
-      <c r="U165" s="51">
+      <c r="U165" s="50">
         <v>226697</v>
       </c>
       <c r="V165" s="8">
@@ -13736,7 +13755,7 @@
       <c r="K178" s="5">
         <v>16088</v>
       </c>
-      <c r="L178" s="51">
+      <c r="L178" s="50">
         <v>8221</v>
       </c>
       <c r="M178" s="5">
@@ -13830,7 +13849,7 @@
       <c r="A180" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="B180" s="51">
+      <c r="B180" s="50">
         <v>2038325</v>
       </c>
       <c r="C180" s="18">
@@ -19360,7 +19379,7 @@
       <c r="L265" s="5">
         <v>1043</v>
       </c>
-      <c r="M265" s="51">
+      <c r="M265" s="50">
         <v>855</v>
       </c>
       <c r="N265" s="5">
@@ -19752,7 +19771,7 @@
       <c r="A272" s="32" t="s">
         <v>272</v>
       </c>
-      <c r="B272" s="51">
+      <c r="B272" s="50">
         <v>373385</v>
       </c>
       <c r="C272" s="33">
@@ -19946,7 +19965,7 @@
         <v>9</v>
       </c>
       <c r="J275" s="5"/>
-      <c r="K275" s="51">
+      <c r="K275" s="50">
         <v>226586</v>
       </c>
       <c r="L275" s="33">

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1895.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1895.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCC9A474-F093-4362-9CBB-72FE98882D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE207B5-49DB-4E0F-B6F2-703972DC6282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="2" r:id="rId1"/>
@@ -1380,7 +1380,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1874904B-D71C-4790-8B63-1651C1F38481}">
   <dimension ref="A2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
@@ -1395,35 +1395,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AN282"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.89453125" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="29.625" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.75" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.375" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.25" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.25" style="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4" style="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10" style="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.5" style="16" customWidth="1"/>
-    <col min="12" max="26" width="6.625" style="16" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="2.75" style="16" customWidth="1"/>
-    <col min="28" max="28" width="9.75" style="16" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="8" style="16" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="2.75" style="16" customWidth="1"/>
-    <col min="32" max="32" width="8.625" style="16" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.625" style="16" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="6.375" style="16" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="2.25" style="16" customWidth="1"/>
-    <col min="36" max="37" width="4" style="16" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="2.5" style="16" customWidth="1"/>
-    <col min="39" max="39" width="4.625" style="16" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="4.125" style="16" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="8.875" style="16"/>
+    <col min="1" max="1" width="31.1015625" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.62890625" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.62890625" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.15625" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.26171875" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.15625" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="4.15625" style="16" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.47265625" style="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.47265625" style="16" customWidth="1"/>
+    <col min="12" max="26" width="7.15625" style="16" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="2.734375" style="16" customWidth="1"/>
+    <col min="28" max="28" width="10.20703125" style="16" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="8.62890625" style="16" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="2.734375" style="16" customWidth="1"/>
+    <col min="32" max="32" width="9.20703125" style="16" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="7.15625" style="16" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="6.734375" style="16" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="2.26171875" style="16" customWidth="1"/>
+    <col min="36" max="37" width="4.15625" style="16" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="2.47265625" style="16" customWidth="1"/>
+    <col min="39" max="39" width="4.7890625" style="16" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.26171875" style="16" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="8.89453125" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="45">
+    <row r="1" spans="1:40" ht="28.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4252,11 +4251,11 @@
         <v>29.992335955168606</v>
       </c>
       <c r="AM42" s="44">
-        <f>AJ42-H42</f>
+        <f t="shared" ref="AM42:AN44" si="0">AJ42-H42</f>
         <v>-0.63944741852103704</v>
       </c>
       <c r="AN42" s="44">
-        <f>AK42-I42</f>
+        <f t="shared" si="0"/>
         <v>-0.4076640448313924</v>
       </c>
     </row>
@@ -4323,11 +4322,11 @@
         <v>24.328172533880362</v>
       </c>
       <c r="AM43" s="38">
-        <f>AJ43-H43</f>
+        <f t="shared" si="0"/>
         <v>1.5683386971886577</v>
       </c>
       <c r="AN43" s="38">
-        <f>AK43-I43</f>
+        <f t="shared" si="0"/>
         <v>-7.1827466119636085E-2</v>
       </c>
     </row>
@@ -4437,11 +4436,11 @@
         <v>24.377942296493838</v>
       </c>
       <c r="AM44" s="38">
-        <f>AJ44-H44</f>
+        <f t="shared" si="0"/>
         <v>3.1725010699259926</v>
       </c>
       <c r="AN44" s="38">
-        <f>AK44-I44</f>
+        <f t="shared" si="0"/>
         <v>1.7779422964938369</v>
       </c>
     </row>
@@ -6427,15 +6426,15 @@
         <v>226434</v>
       </c>
       <c r="AF74" s="43">
-        <f>AB74-B74</f>
+        <f t="shared" ref="AF74:AH75" si="1">AB74-B74</f>
         <v>-10419</v>
       </c>
       <c r="AG74" s="43">
-        <f>AC74-C74</f>
+        <f t="shared" si="1"/>
         <v>-1160</v>
       </c>
       <c r="AH74" s="43">
-        <f>AD74-D74</f>
+        <f t="shared" si="1"/>
         <v>-25</v>
       </c>
       <c r="AJ74" s="44">
@@ -6533,15 +6532,15 @@
         <v>13080</v>
       </c>
       <c r="AF75" s="37">
-        <f>AB75-B75</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AG75" s="37">
-        <f>AC75-C75</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AH75" s="37">
-        <f>AD75-D75</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AJ75" s="38">
@@ -7107,15 +7106,15 @@
         <v>47547</v>
       </c>
       <c r="AF84" s="43">
-        <f>AB84-B84</f>
+        <f t="shared" ref="AF84:AH85" si="2">AB84-B84</f>
         <v>9</v>
       </c>
       <c r="AG84" s="43">
-        <f>AC84-C84</f>
+        <f t="shared" si="2"/>
         <v>15180</v>
       </c>
       <c r="AH84" s="43">
-        <f>AD84-D84</f>
+        <f t="shared" si="2"/>
         <v>-40</v>
       </c>
       <c r="AJ84" s="44">
@@ -7209,15 +7208,15 @@
         <v>49718</v>
       </c>
       <c r="AF85" s="37">
-        <f>AB85-B85</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AG85" s="37">
-        <f>AC85-C85</f>
+        <f t="shared" si="2"/>
         <v>200</v>
       </c>
       <c r="AH85" s="37">
-        <f>AD85-D85</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ85" s="38">
@@ -14261,15 +14260,15 @@
       <c r="Y183" s="18"/>
       <c r="Z183" s="18"/>
       <c r="AB183" s="37">
-        <f>B183</f>
+        <f t="shared" ref="AB183:AD184" si="3">B183</f>
         <v>78483</v>
       </c>
       <c r="AC183" s="37">
-        <f>C183</f>
+        <f t="shared" si="3"/>
         <v>3486</v>
       </c>
       <c r="AD183" s="37">
-        <f>D183</f>
+        <f t="shared" si="3"/>
         <v>2355</v>
       </c>
       <c r="AF183" s="39"/>
@@ -14326,15 +14325,15 @@
       <c r="Y184" s="18"/>
       <c r="Z184" s="18"/>
       <c r="AB184" s="37">
-        <f>B184</f>
+        <f t="shared" si="3"/>
         <v>357365</v>
       </c>
       <c r="AC184" s="37">
-        <f>C184</f>
+        <f t="shared" si="3"/>
         <v>11937</v>
       </c>
       <c r="AD184" s="37">
-        <f>D184</f>
+        <f t="shared" si="3"/>
         <v>8253</v>
       </c>
       <c r="AF184" s="39"/>
@@ -14867,15 +14866,15 @@
         <v>2424048</v>
       </c>
       <c r="AF191" s="43">
-        <f>AB191-B191</f>
+        <f t="shared" ref="AF191:AH192" si="4">AB191-B191</f>
         <v>95839</v>
       </c>
       <c r="AG191" s="43">
-        <f>AC191-C191</f>
+        <f t="shared" si="4"/>
         <v>-10747</v>
       </c>
       <c r="AH191" s="43">
-        <f>AD191-D191</f>
+        <f t="shared" si="4"/>
         <v>38131</v>
       </c>
       <c r="AJ191" s="44">
@@ -14971,15 +14970,15 @@
         <v>88366</v>
       </c>
       <c r="AF192" s="37">
-        <f>AB192-B192</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AG192" s="37">
-        <f>AC192-C192</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AH192" s="37">
-        <f>AD192-D192</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AJ192" s="38">
@@ -15155,15 +15154,15 @@
         <v>3433421</v>
       </c>
       <c r="AF195" s="43">
-        <f>AB195-B195</f>
+        <f t="shared" ref="AF195:AH196" si="5">AB195-B195</f>
         <v>24521</v>
       </c>
       <c r="AG195" s="43">
-        <f>AC195-C195</f>
+        <f t="shared" si="5"/>
         <v>723273</v>
       </c>
       <c r="AH195" s="43">
-        <f>AD195-D195</f>
+        <f t="shared" si="5"/>
         <v>47936</v>
       </c>
       <c r="AJ195" s="44">
@@ -15253,15 +15252,15 @@
         <v>12644</v>
       </c>
       <c r="AF196" s="37">
-        <f>AB196-B196</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AG196" s="37">
-        <f>AC196-C196</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AH196" s="37">
-        <f>AD196-D196</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AJ196" s="38">
@@ -15577,44 +15576,58 @@
     </row>
     <row r="202" spans="1:40">
       <c r="A202" s="26" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B202" s="27">
-        <v>70892</v>
+        <v>827879</v>
       </c>
       <c r="C202" s="27">
-        <v>3752</v>
+        <v>21773</v>
       </c>
       <c r="D202" s="27">
-        <v>3320</v>
+        <v>12900</v>
       </c>
       <c r="E202" s="27">
-        <v>2517</v>
+        <v>88111</v>
       </c>
       <c r="F202" s="27">
-        <v>108</v>
+        <v>2439</v>
       </c>
       <c r="G202" s="27">
-        <v>47</v>
-      </c>
-      <c r="H202" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="I202" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="J202" s="28" t="s">
-        <v>221</v>
-      </c>
+        <v>1558</v>
+      </c>
+      <c r="H202" s="28">
+        <v>23.4</v>
+      </c>
+      <c r="I202" s="28">
+        <v>14</v>
+      </c>
+      <c r="J202" s="28"/>
       <c r="K202" s="5"/>
-      <c r="L202" s="27"/>
-      <c r="M202" s="27"/>
-      <c r="N202" s="27"/>
-      <c r="O202" s="27"/>
-      <c r="P202" s="27"/>
-      <c r="Q202" s="27"/>
-      <c r="R202" s="27"/>
-      <c r="S202" s="27"/>
+      <c r="L202" s="27">
+        <v>144597</v>
+      </c>
+      <c r="M202" s="27">
+        <v>60092</v>
+      </c>
+      <c r="N202" s="27">
+        <v>54757</v>
+      </c>
+      <c r="O202" s="27">
+        <v>61486</v>
+      </c>
+      <c r="P202" s="27">
+        <v>138486</v>
+      </c>
+      <c r="Q202" s="27">
+        <v>99948</v>
+      </c>
+      <c r="R202" s="27">
+        <v>120749</v>
+      </c>
+      <c r="S202" s="27">
+        <v>147764</v>
+      </c>
       <c r="T202" s="27"/>
       <c r="U202" s="27"/>
       <c r="V202" s="27"/>
@@ -15623,136 +15636,99 @@
       <c r="Y202" s="27"/>
       <c r="Z202" s="27"/>
       <c r="AB202" s="37">
-        <f>B202</f>
-        <v>70892</v>
+        <f>SUM(L202:Z202)</f>
+        <v>827879</v>
       </c>
       <c r="AC202" s="37">
-        <f>C202</f>
-        <v>3752</v>
+        <f>SUM(L203:Z203)</f>
+        <v>21773</v>
       </c>
       <c r="AD202" s="37">
-        <f>D202</f>
-        <v>3320</v>
-      </c>
-      <c r="AF202" s="39"/>
-      <c r="AG202" s="39"/>
-      <c r="AH202" s="39"/>
+        <f>SUM(L204:Z204)</f>
+        <v>12898</v>
+      </c>
+      <c r="AF202" s="37">
+        <f>AB202-B202</f>
+        <v>0</v>
+      </c>
+      <c r="AG202" s="37">
+        <f>AC202-C202</f>
+        <v>0</v>
+      </c>
+      <c r="AH202" s="37">
+        <f>AD202-D202</f>
+        <v>-2</v>
+      </c>
       <c r="AJ202" s="38">
         <f>C202/B202*1000</f>
-        <v>52.925576933927665</v>
+        <v>26.299737038866791</v>
       </c>
       <c r="AK202" s="38">
         <f>D202/B202*1000</f>
-        <v>46.831800485245161</v>
-      </c>
-      <c r="AM202" s="38"/>
-      <c r="AN202" s="38"/>
+        <v>15.581987222770477</v>
+      </c>
+      <c r="AM202" s="38">
+        <f>AJ202-H202</f>
+        <v>2.8997370388667925</v>
+      </c>
+      <c r="AN202" s="38">
+        <f>AK202-I202</f>
+        <v>1.5819872227704774</v>
+      </c>
     </row>
     <row r="203" spans="1:40">
-      <c r="A203" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="B203" s="27">
-        <v>827879</v>
-      </c>
-      <c r="C203" s="27">
-        <v>21773</v>
-      </c>
-      <c r="D203" s="27">
-        <v>12900</v>
-      </c>
-      <c r="E203" s="27">
-        <v>88111</v>
-      </c>
-      <c r="F203" s="27">
-        <v>2439</v>
-      </c>
-      <c r="G203" s="27">
-        <v>1558</v>
-      </c>
-      <c r="H203" s="28">
-        <v>23.4</v>
-      </c>
-      <c r="I203" s="28">
-        <v>14</v>
-      </c>
-      <c r="J203" s="28"/>
+      <c r="A203" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B203" s="5"/>
+      <c r="C203" s="5"/>
+      <c r="D203" s="5"/>
+      <c r="E203" s="5"/>
+      <c r="F203" s="5"/>
+      <c r="G203" s="5"/>
+      <c r="H203" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I203" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J203" s="6"/>
       <c r="K203" s="5"/>
-      <c r="L203" s="27">
-        <v>144597</v>
-      </c>
-      <c r="M203" s="27">
-        <v>60092</v>
-      </c>
-      <c r="N203" s="27">
-        <v>54757</v>
-      </c>
-      <c r="O203" s="27">
-        <v>61486</v>
-      </c>
-      <c r="P203" s="27">
-        <v>138486</v>
-      </c>
-      <c r="Q203" s="27">
-        <v>99948</v>
-      </c>
-      <c r="R203" s="27">
-        <v>120749</v>
-      </c>
-      <c r="S203" s="27">
-        <v>147764</v>
-      </c>
-      <c r="T203" s="27"/>
-      <c r="U203" s="27"/>
-      <c r="V203" s="27"/>
-      <c r="W203" s="27"/>
-      <c r="X203" s="27"/>
-      <c r="Y203" s="27"/>
-      <c r="Z203" s="27"/>
-      <c r="AB203" s="37">
-        <f>SUM(L203:Z203)</f>
-        <v>827879</v>
-      </c>
-      <c r="AC203" s="37">
-        <f>SUM(L204:Z204)</f>
-        <v>21773</v>
-      </c>
-      <c r="AD203" s="37">
-        <f>SUM(L205:Z205)</f>
-        <v>12898</v>
-      </c>
-      <c r="AF203" s="37">
-        <f>AB203-B203</f>
-        <v>0</v>
-      </c>
-      <c r="AG203" s="37">
-        <f>AC203-C203</f>
-        <v>0</v>
-      </c>
-      <c r="AH203" s="37">
-        <f>AD203-D203</f>
-        <v>-2</v>
-      </c>
-      <c r="AJ203" s="38">
-        <f>C203/B203*1000</f>
-        <v>26.299737038866791</v>
-      </c>
-      <c r="AK203" s="38">
-        <f>D203/B203*1000</f>
-        <v>15.581987222770477</v>
-      </c>
-      <c r="AM203" s="38">
-        <f>AJ203-H203</f>
-        <v>2.8997370388667925</v>
-      </c>
-      <c r="AN203" s="38">
-        <f>AK203-I203</f>
-        <v>1.5819872227704774</v>
-      </c>
+      <c r="L203" s="5">
+        <v>3207</v>
+      </c>
+      <c r="M203" s="5">
+        <v>1850</v>
+      </c>
+      <c r="N203" s="5">
+        <v>1203</v>
+      </c>
+      <c r="O203" s="5">
+        <v>1318</v>
+      </c>
+      <c r="P203" s="5">
+        <v>3485</v>
+      </c>
+      <c r="Q203" s="5">
+        <v>3624</v>
+      </c>
+      <c r="R203" s="5">
+        <v>3946</v>
+      </c>
+      <c r="S203" s="5">
+        <v>3140</v>
+      </c>
+      <c r="T203" s="5"/>
+      <c r="U203" s="5"/>
+      <c r="V203" s="5"/>
+      <c r="W203" s="5"/>
+      <c r="X203" s="5"/>
+      <c r="Y203" s="5"/>
+      <c r="Z203" s="5"/>
     </row>
     <row r="204" spans="1:40">
       <c r="A204" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
@@ -15769,28 +15745,28 @@
       <c r="J204" s="6"/>
       <c r="K204" s="5"/>
       <c r="L204" s="5">
-        <v>3207</v>
+        <v>1548</v>
       </c>
       <c r="M204" s="5">
-        <v>1850</v>
+        <v>1325</v>
       </c>
       <c r="N204" s="5">
-        <v>1203</v>
+        <v>585</v>
       </c>
       <c r="O204" s="5">
-        <v>1318</v>
+        <v>901</v>
       </c>
       <c r="P204" s="5">
-        <v>3485</v>
+        <v>1535</v>
       </c>
       <c r="Q204" s="5">
-        <v>3624</v>
+        <v>1809</v>
       </c>
       <c r="R204" s="5">
-        <v>3946</v>
+        <v>3579</v>
       </c>
       <c r="S204" s="5">
-        <v>3140</v>
+        <v>1616</v>
       </c>
       <c r="T204" s="5"/>
       <c r="U204" s="5"/>
@@ -15801,146 +15777,138 @@
       <c r="Z204" s="5"/>
     </row>
     <row r="205" spans="1:40">
-      <c r="A205" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B205" s="5"/>
-      <c r="C205" s="5"/>
-      <c r="D205" s="5"/>
-      <c r="E205" s="5"/>
-      <c r="F205" s="5"/>
-      <c r="G205" s="5"/>
-      <c r="H205" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="I205" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J205" s="6"/>
+      <c r="A205" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="B205" s="27">
+        <v>216249</v>
+      </c>
+      <c r="C205" s="27">
+        <v>7715</v>
+      </c>
+      <c r="D205" s="27">
+        <v>3561</v>
+      </c>
+      <c r="E205" s="27">
+        <v>4710</v>
+      </c>
+      <c r="F205" s="27">
+        <v>211</v>
+      </c>
+      <c r="G205" s="27">
+        <v>150</v>
+      </c>
+      <c r="H205" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="I205" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J205" s="28"/>
       <c r="K205" s="5"/>
-      <c r="L205" s="5">
-        <v>1548</v>
-      </c>
-      <c r="M205" s="5">
-        <v>1325</v>
-      </c>
-      <c r="N205" s="5">
-        <v>585</v>
-      </c>
-      <c r="O205" s="5">
-        <v>901</v>
-      </c>
-      <c r="P205" s="5">
-        <v>1535</v>
-      </c>
-      <c r="Q205" s="5">
-        <v>1809</v>
-      </c>
-      <c r="R205" s="5">
-        <v>3579</v>
-      </c>
-      <c r="S205" s="5">
-        <v>1616</v>
-      </c>
-      <c r="T205" s="5"/>
-      <c r="U205" s="5"/>
-      <c r="V205" s="5"/>
-      <c r="W205" s="5"/>
-      <c r="X205" s="5"/>
-      <c r="Y205" s="5"/>
-      <c r="Z205" s="5"/>
+      <c r="L205" s="27">
+        <v>99355</v>
+      </c>
+      <c r="M205" s="27">
+        <v>51021</v>
+      </c>
+      <c r="N205" s="27">
+        <v>41830</v>
+      </c>
+      <c r="O205" s="27">
+        <v>24043</v>
+      </c>
+      <c r="P205" s="27"/>
+      <c r="Q205" s="27"/>
+      <c r="R205" s="27"/>
+      <c r="S205" s="27"/>
+      <c r="T205" s="27"/>
+      <c r="U205" s="27"/>
+      <c r="V205" s="27"/>
+      <c r="W205" s="27"/>
+      <c r="X205" s="27"/>
+      <c r="Y205" s="27"/>
+      <c r="Z205" s="27"/>
+      <c r="AB205" s="37">
+        <f>SUM(L205:Z205)</f>
+        <v>216249</v>
+      </c>
+      <c r="AC205" s="37">
+        <f>SUM(L206:Z206)</f>
+        <v>7715</v>
+      </c>
+      <c r="AD205" s="37">
+        <f>SUM(L207:Z207)</f>
+        <v>3561</v>
+      </c>
+      <c r="AF205" s="37">
+        <f>AB205-B205</f>
+        <v>0</v>
+      </c>
+      <c r="AG205" s="37">
+        <f>AC205-C205</f>
+        <v>0</v>
+      </c>
+      <c r="AH205" s="37">
+        <f>AD205-D205</f>
+        <v>0</v>
+      </c>
+      <c r="AJ205" s="38">
+        <f>C205/B205*1000</f>
+        <v>35.676465555910085</v>
+      </c>
+      <c r="AK205" s="38">
+        <f>D205/B205*1000</f>
+        <v>16.46712817169097</v>
+      </c>
+      <c r="AM205" s="38"/>
+      <c r="AN205" s="38"/>
     </row>
     <row r="206" spans="1:40">
-      <c r="A206" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="B206" s="27">
-        <v>216249</v>
-      </c>
-      <c r="C206" s="27">
-        <v>7715</v>
-      </c>
-      <c r="D206" s="27">
-        <v>3561</v>
-      </c>
-      <c r="E206" s="27">
-        <v>4710</v>
-      </c>
-      <c r="F206" s="27">
-        <v>211</v>
-      </c>
-      <c r="G206" s="27">
-        <v>150</v>
-      </c>
-      <c r="H206" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="I206" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="J206" s="28"/>
+      <c r="A206" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B206" s="5"/>
+      <c r="C206" s="5"/>
+      <c r="D206" s="5"/>
+      <c r="E206" s="5"/>
+      <c r="F206" s="5"/>
+      <c r="G206" s="5"/>
+      <c r="H206" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I206" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J206" s="6"/>
       <c r="K206" s="5"/>
-      <c r="L206" s="27">
-        <v>99355</v>
-      </c>
-      <c r="M206" s="27">
-        <v>51021</v>
-      </c>
-      <c r="N206" s="27">
-        <v>41830</v>
-      </c>
-      <c r="O206" s="27">
-        <v>24043</v>
-      </c>
-      <c r="P206" s="27"/>
-      <c r="Q206" s="27"/>
-      <c r="R206" s="27"/>
-      <c r="S206" s="27"/>
-      <c r="T206" s="27"/>
-      <c r="U206" s="27"/>
-      <c r="V206" s="27"/>
-      <c r="W206" s="27"/>
-      <c r="X206" s="27"/>
-      <c r="Y206" s="27"/>
-      <c r="Z206" s="27"/>
-      <c r="AB206" s="37">
-        <f>SUM(L206:Z206)</f>
-        <v>216249</v>
-      </c>
-      <c r="AC206" s="37">
-        <f>SUM(L207:Z207)</f>
-        <v>7715</v>
-      </c>
-      <c r="AD206" s="37">
-        <f>SUM(L208:Z208)</f>
-        <v>3561</v>
-      </c>
-      <c r="AF206" s="37">
-        <f>AB206-B206</f>
-        <v>0</v>
-      </c>
-      <c r="AG206" s="37">
-        <f>AC206-C206</f>
-        <v>0</v>
-      </c>
-      <c r="AH206" s="37">
-        <f>AD206-D206</f>
-        <v>0</v>
-      </c>
-      <c r="AJ206" s="38">
-        <f>C206/B206*1000</f>
-        <v>35.676465555910085</v>
-      </c>
-      <c r="AK206" s="38">
-        <f>D206/B206*1000</f>
-        <v>16.46712817169097</v>
-      </c>
-      <c r="AM206" s="38"/>
-      <c r="AN206" s="38"/>
+      <c r="L206" s="5">
+        <v>3697</v>
+      </c>
+      <c r="M206" s="5">
+        <v>1604</v>
+      </c>
+      <c r="N206" s="5">
+        <v>1557</v>
+      </c>
+      <c r="O206" s="5">
+        <v>857</v>
+      </c>
+      <c r="P206" s="5"/>
+      <c r="Q206" s="5"/>
+      <c r="R206" s="5"/>
+      <c r="S206" s="5"/>
+      <c r="T206" s="5"/>
+      <c r="U206" s="5"/>
+      <c r="V206" s="5"/>
+      <c r="W206" s="5"/>
+      <c r="X206" s="5"/>
+      <c r="Y206" s="5"/>
+      <c r="Z206" s="5"/>
     </row>
     <row r="207" spans="1:40">
       <c r="A207" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
@@ -15957,16 +15925,16 @@
       <c r="J207" s="6"/>
       <c r="K207" s="5"/>
       <c r="L207" s="5">
-        <v>3697</v>
+        <v>1647</v>
       </c>
       <c r="M207" s="5">
-        <v>1604</v>
+        <v>641</v>
       </c>
       <c r="N207" s="5">
-        <v>1557</v>
+        <v>851</v>
       </c>
       <c r="O207" s="5">
-        <v>857</v>
+        <v>422</v>
       </c>
       <c r="P207" s="5"/>
       <c r="Q207" s="5"/>
@@ -15981,152 +15949,160 @@
       <c r="Z207" s="5"/>
     </row>
     <row r="208" spans="1:40">
-      <c r="A208" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="B208" s="5"/>
-      <c r="C208" s="5"/>
-      <c r="D208" s="5"/>
-      <c r="E208" s="5"/>
-      <c r="F208" s="5"/>
-      <c r="G208" s="5"/>
-      <c r="H208" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="I208" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J208" s="6"/>
+      <c r="A208" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="B208" s="27">
+        <v>1693581</v>
+      </c>
+      <c r="C208" s="27">
+        <v>110986</v>
+      </c>
+      <c r="D208" s="27">
+        <v>74990</v>
+      </c>
+      <c r="E208" s="27">
+        <v>202201</v>
+      </c>
+      <c r="F208" s="27">
+        <v>7852</v>
+      </c>
+      <c r="G208" s="27">
+        <v>5127</v>
+      </c>
+      <c r="H208" s="28">
+        <v>55.3</v>
+      </c>
+      <c r="I208" s="28">
+        <v>41.8</v>
+      </c>
+      <c r="J208" s="28"/>
       <c r="K208" s="5"/>
-      <c r="L208" s="5">
-        <v>1647</v>
-      </c>
-      <c r="M208" s="5">
-        <v>641</v>
-      </c>
-      <c r="N208" s="5">
-        <v>851</v>
-      </c>
-      <c r="O208" s="5">
-        <v>422</v>
-      </c>
-      <c r="P208" s="5"/>
-      <c r="Q208" s="5"/>
-      <c r="R208" s="5"/>
-      <c r="S208" s="5"/>
-      <c r="T208" s="5"/>
-      <c r="U208" s="5"/>
-      <c r="V208" s="5"/>
-      <c r="W208" s="5"/>
-      <c r="X208" s="5"/>
-      <c r="Y208" s="5"/>
-      <c r="Z208" s="5"/>
+      <c r="L208" s="27">
+        <v>235735</v>
+      </c>
+      <c r="M208" s="27">
+        <v>184372</v>
+      </c>
+      <c r="N208" s="27">
+        <v>248388</v>
+      </c>
+      <c r="O208" s="27">
+        <v>208530</v>
+      </c>
+      <c r="P208" s="27">
+        <v>227234</v>
+      </c>
+      <c r="Q208" s="27">
+        <v>258697</v>
+      </c>
+      <c r="R208" s="27">
+        <v>270274</v>
+      </c>
+      <c r="S208" s="27">
+        <v>60851</v>
+      </c>
+      <c r="T208" s="27"/>
+      <c r="U208" s="27"/>
+      <c r="V208" s="27"/>
+      <c r="W208" s="27"/>
+      <c r="X208" s="27"/>
+      <c r="Y208" s="27"/>
+      <c r="Z208" s="27"/>
+      <c r="AB208" s="37">
+        <f>SUM(L208:Z208)</f>
+        <v>1694081</v>
+      </c>
+      <c r="AC208" s="37">
+        <f>SUM(L209:Z209)</f>
+        <v>110986</v>
+      </c>
+      <c r="AD208" s="37">
+        <f>SUM(L210:Z210)</f>
+        <v>74990</v>
+      </c>
+      <c r="AF208" s="37">
+        <f>AB208-B208</f>
+        <v>500</v>
+      </c>
+      <c r="AG208" s="37">
+        <f>AC208-C208</f>
+        <v>0</v>
+      </c>
+      <c r="AH208" s="37">
+        <f>AD208-D208</f>
+        <v>0</v>
+      </c>
+      <c r="AJ208" s="38">
+        <f>C208/B208*1000</f>
+        <v>65.533328491521814</v>
+      </c>
+      <c r="AK208" s="38">
+        <f>D208/B208*1000</f>
+        <v>44.278956837612135</v>
+      </c>
+      <c r="AM208" s="38">
+        <f>AJ208-H208</f>
+        <v>10.233328491521817</v>
+      </c>
+      <c r="AN208" s="38">
+        <f>AK208-I208</f>
+        <v>2.478956837612138</v>
+      </c>
     </row>
     <row r="209" spans="1:40">
-      <c r="A209" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="B209" s="27">
-        <v>1693581</v>
-      </c>
-      <c r="C209" s="27">
-        <v>110986</v>
-      </c>
-      <c r="D209" s="27">
-        <v>74990</v>
-      </c>
-      <c r="E209" s="27">
-        <v>202201</v>
-      </c>
-      <c r="F209" s="27">
-        <v>7852</v>
-      </c>
-      <c r="G209" s="27">
-        <v>5127</v>
-      </c>
-      <c r="H209" s="28">
-        <v>55.3</v>
-      </c>
-      <c r="I209" s="28">
-        <v>41.8</v>
-      </c>
-      <c r="J209" s="28"/>
+      <c r="A209" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B209" s="5"/>
+      <c r="C209" s="5"/>
+      <c r="D209" s="5"/>
+      <c r="E209" s="5"/>
+      <c r="F209" s="5"/>
+      <c r="G209" s="5"/>
+      <c r="H209" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I209" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J209" s="6"/>
       <c r="K209" s="5"/>
-      <c r="L209" s="27">
-        <v>235735</v>
-      </c>
-      <c r="M209" s="27">
-        <v>184372</v>
-      </c>
-      <c r="N209" s="27">
-        <v>248388</v>
-      </c>
-      <c r="O209" s="27">
-        <v>208530</v>
-      </c>
-      <c r="P209" s="27">
-        <v>227234</v>
-      </c>
-      <c r="Q209" s="27">
-        <v>258697</v>
-      </c>
-      <c r="R209" s="27">
-        <v>270274</v>
-      </c>
-      <c r="S209" s="27">
-        <v>60851</v>
-      </c>
-      <c r="T209" s="27"/>
-      <c r="U209" s="27"/>
-      <c r="V209" s="27"/>
-      <c r="W209" s="27"/>
-      <c r="X209" s="27"/>
-      <c r="Y209" s="27"/>
-      <c r="Z209" s="27"/>
-      <c r="AB209" s="37">
-        <f>SUM(L209:Z209)</f>
-        <v>1694081</v>
-      </c>
-      <c r="AC209" s="37">
-        <f>SUM(L210:Z210)</f>
-        <v>110986</v>
-      </c>
-      <c r="AD209" s="37">
-        <f>SUM(L211:Z211)</f>
-        <v>74990</v>
-      </c>
-      <c r="AF209" s="37">
-        <f>AB209-B209</f>
-        <v>500</v>
-      </c>
-      <c r="AG209" s="37">
-        <f>AC209-C209</f>
-        <v>0</v>
-      </c>
-      <c r="AH209" s="37">
-        <f>AD209-D209</f>
-        <v>0</v>
-      </c>
-      <c r="AJ209" s="38">
-        <f>C209/B209*1000</f>
-        <v>65.533328491521814</v>
-      </c>
-      <c r="AK209" s="38">
-        <f>D209/B209*1000</f>
-        <v>44.278956837612135</v>
-      </c>
-      <c r="AM209" s="38">
-        <f>AJ209-H209</f>
-        <v>10.233328491521817</v>
-      </c>
-      <c r="AN209" s="38">
-        <f>AK209-I209</f>
-        <v>2.478956837612138</v>
-      </c>
+      <c r="L209" s="5">
+        <v>13496</v>
+      </c>
+      <c r="M209" s="5">
+        <v>11454</v>
+      </c>
+      <c r="N209" s="5">
+        <v>15722</v>
+      </c>
+      <c r="O209" s="5">
+        <v>15787</v>
+      </c>
+      <c r="P209" s="5">
+        <v>20314</v>
+      </c>
+      <c r="Q209" s="5">
+        <v>13688</v>
+      </c>
+      <c r="R209" s="5">
+        <v>18487</v>
+      </c>
+      <c r="S209" s="5">
+        <v>2038</v>
+      </c>
+      <c r="T209" s="5"/>
+      <c r="U209" s="5"/>
+      <c r="V209" s="5"/>
+      <c r="W209" s="5"/>
+      <c r="X209" s="5"/>
+      <c r="Y209" s="5"/>
+      <c r="Z209" s="5"/>
     </row>
     <row r="210" spans="1:40">
       <c r="A210" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
@@ -16143,28 +16119,28 @@
       <c r="J210" s="6"/>
       <c r="K210" s="5"/>
       <c r="L210" s="5">
-        <v>13496</v>
+        <v>9604</v>
       </c>
       <c r="M210" s="5">
-        <v>11454</v>
+        <v>6611</v>
       </c>
       <c r="N210" s="5">
-        <v>15722</v>
+        <v>9415</v>
       </c>
       <c r="O210" s="5">
-        <v>15787</v>
+        <v>11154</v>
       </c>
       <c r="P210" s="5">
-        <v>20314</v>
+        <v>17087</v>
       </c>
       <c r="Q210" s="5">
-        <v>13688</v>
+        <v>10649</v>
       </c>
       <c r="R210" s="5">
-        <v>18487</v>
+        <v>9038</v>
       </c>
       <c r="S210" s="5">
-        <v>2038</v>
+        <v>1432</v>
       </c>
       <c r="T210" s="5"/>
       <c r="U210" s="5"/>
@@ -16175,164 +16151,168 @@
       <c r="Z210" s="5"/>
     </row>
     <row r="211" spans="1:40">
-      <c r="A211" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B211" s="5"/>
-      <c r="C211" s="5"/>
-      <c r="D211" s="5"/>
-      <c r="E211" s="5"/>
-      <c r="F211" s="5"/>
-      <c r="G211" s="5"/>
-      <c r="H211" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="I211" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J211" s="6"/>
+      <c r="A211" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="B211" s="27">
+        <v>1088321</v>
+      </c>
+      <c r="C211" s="27">
+        <v>32163</v>
+      </c>
+      <c r="D211" s="27">
+        <v>17530</v>
+      </c>
+      <c r="E211" s="27">
+        <v>49684</v>
+      </c>
+      <c r="F211" s="27">
+        <v>1645</v>
+      </c>
+      <c r="G211" s="27">
+        <v>952</v>
+      </c>
+      <c r="H211" s="28">
+        <v>29.6</v>
+      </c>
+      <c r="I211" s="28">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="J211" s="28"/>
       <c r="K211" s="5"/>
-      <c r="L211" s="5">
-        <v>9604</v>
-      </c>
-      <c r="M211" s="5">
-        <v>6611</v>
-      </c>
-      <c r="N211" s="5">
-        <v>9415</v>
-      </c>
-      <c r="O211" s="5">
-        <v>11154</v>
-      </c>
-      <c r="P211" s="5">
-        <v>17087</v>
-      </c>
-      <c r="Q211" s="5">
-        <v>10649</v>
-      </c>
-      <c r="R211" s="5">
-        <v>9038</v>
-      </c>
-      <c r="S211" s="5">
-        <v>1432</v>
-      </c>
-      <c r="T211" s="5"/>
-      <c r="U211" s="5"/>
-      <c r="V211" s="5"/>
-      <c r="W211" s="5"/>
-      <c r="X211" s="5"/>
-      <c r="Y211" s="5"/>
-      <c r="Z211" s="5"/>
+      <c r="L211" s="27">
+        <v>204164</v>
+      </c>
+      <c r="M211" s="27">
+        <v>54715</v>
+      </c>
+      <c r="N211" s="27">
+        <v>73335</v>
+      </c>
+      <c r="O211" s="27">
+        <v>110913</v>
+      </c>
+      <c r="P211" s="27">
+        <v>51910</v>
+      </c>
+      <c r="Q211" s="27">
+        <v>87230</v>
+      </c>
+      <c r="R211" s="27">
+        <v>75155</v>
+      </c>
+      <c r="S211" s="27">
+        <v>113930</v>
+      </c>
+      <c r="T211" s="27">
+        <v>130019</v>
+      </c>
+      <c r="U211" s="27">
+        <v>186950</v>
+      </c>
+      <c r="V211" s="27"/>
+      <c r="W211" s="27"/>
+      <c r="X211" s="27"/>
+      <c r="Y211" s="27"/>
+      <c r="Z211" s="27"/>
+      <c r="AB211" s="37">
+        <f>SUM(L211:Z211)</f>
+        <v>1088321</v>
+      </c>
+      <c r="AC211" s="37">
+        <f>SUM(L212:Z212)</f>
+        <v>32163</v>
+      </c>
+      <c r="AD211" s="37">
+        <f>SUM(L213:Z213)</f>
+        <v>17530</v>
+      </c>
+      <c r="AF211" s="37">
+        <f>AB211-B211</f>
+        <v>0</v>
+      </c>
+      <c r="AG211" s="37">
+        <f>AC211-C211</f>
+        <v>0</v>
+      </c>
+      <c r="AH211" s="37">
+        <f>AD211-D211</f>
+        <v>0</v>
+      </c>
+      <c r="AJ211" s="38">
+        <f>C211/B211*1000</f>
+        <v>29.552861701648688</v>
+      </c>
+      <c r="AK211" s="38">
+        <f>D211/B211*1000</f>
+        <v>16.107380083633412</v>
+      </c>
+      <c r="AM211" s="38">
+        <f>AJ211-H211</f>
+        <v>-4.7138298351313779E-2</v>
+      </c>
+      <c r="AN211" s="38">
+        <f>AK211-I211</f>
+        <v>7.3800836334108055E-3</v>
+      </c>
     </row>
     <row r="212" spans="1:40">
-      <c r="A212" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="B212" s="27">
-        <v>1088321</v>
-      </c>
-      <c r="C212" s="27">
-        <v>32163</v>
-      </c>
-      <c r="D212" s="27">
-        <v>17530</v>
-      </c>
-      <c r="E212" s="27">
-        <v>49684</v>
-      </c>
-      <c r="F212" s="27">
-        <v>1645</v>
-      </c>
-      <c r="G212" s="27">
-        <v>952</v>
-      </c>
-      <c r="H212" s="28">
-        <v>29.6</v>
-      </c>
-      <c r="I212" s="28">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="J212" s="28"/>
+      <c r="A212" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B212" s="5"/>
+      <c r="C212" s="5"/>
+      <c r="D212" s="5"/>
+      <c r="E212" s="5"/>
+      <c r="F212" s="5"/>
+      <c r="G212" s="5"/>
+      <c r="H212" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I212" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J212" s="6"/>
       <c r="K212" s="5"/>
-      <c r="L212" s="27">
-        <v>204164</v>
-      </c>
-      <c r="M212" s="27">
-        <v>54715</v>
-      </c>
-      <c r="N212" s="27">
-        <v>73335</v>
-      </c>
-      <c r="O212" s="27">
-        <v>110913</v>
-      </c>
-      <c r="P212" s="27">
-        <v>51910</v>
-      </c>
-      <c r="Q212" s="27">
-        <v>87230</v>
-      </c>
-      <c r="R212" s="27">
-        <v>75155</v>
-      </c>
-      <c r="S212" s="27">
-        <v>113930</v>
-      </c>
-      <c r="T212" s="27">
-        <v>130019</v>
-      </c>
-      <c r="U212" s="27">
-        <v>186950</v>
-      </c>
-      <c r="V212" s="27"/>
-      <c r="W212" s="27"/>
-      <c r="X212" s="27"/>
-      <c r="Y212" s="27"/>
-      <c r="Z212" s="27"/>
-      <c r="AB212" s="37">
-        <f>SUM(L212:Z212)</f>
-        <v>1088321</v>
-      </c>
-      <c r="AC212" s="37">
-        <f>SUM(L213:Z213)</f>
-        <v>32163</v>
-      </c>
-      <c r="AD212" s="37">
-        <f>SUM(L214:Z214)</f>
-        <v>17530</v>
-      </c>
-      <c r="AF212" s="37">
-        <f>AB212-B212</f>
-        <v>0</v>
-      </c>
-      <c r="AG212" s="37">
-        <f>AC212-C212</f>
-        <v>0</v>
-      </c>
-      <c r="AH212" s="37">
-        <f>AD212-D212</f>
-        <v>0</v>
-      </c>
-      <c r="AJ212" s="38">
-        <f>C212/B212*1000</f>
-        <v>29.552861701648688</v>
-      </c>
-      <c r="AK212" s="38">
-        <f>D212/B212*1000</f>
-        <v>16.107380083633412</v>
-      </c>
-      <c r="AM212" s="38">
-        <f>AJ212-H212</f>
-        <v>-4.7138298351313779E-2</v>
-      </c>
-      <c r="AN212" s="38">
-        <f>AK212-I212</f>
-        <v>7.3800836334108055E-3</v>
-      </c>
+      <c r="L212" s="5">
+        <v>6518</v>
+      </c>
+      <c r="M212" s="5">
+        <v>1926</v>
+      </c>
+      <c r="N212" s="5">
+        <v>1633</v>
+      </c>
+      <c r="O212" s="5">
+        <v>3177</v>
+      </c>
+      <c r="P212" s="5">
+        <v>1503</v>
+      </c>
+      <c r="Q212" s="5">
+        <v>3195</v>
+      </c>
+      <c r="R212" s="5">
+        <v>2368</v>
+      </c>
+      <c r="S212" s="5">
+        <v>3674</v>
+      </c>
+      <c r="T212" s="5">
+        <v>3174</v>
+      </c>
+      <c r="U212" s="5">
+        <v>4995</v>
+      </c>
+      <c r="V212" s="5"/>
+      <c r="W212" s="5"/>
+      <c r="X212" s="5"/>
+      <c r="Y212" s="5"/>
+      <c r="Z212" s="5"/>
     </row>
     <row r="213" spans="1:40">
       <c r="A213" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
@@ -16349,34 +16329,34 @@
       <c r="J213" s="6"/>
       <c r="K213" s="5"/>
       <c r="L213" s="5">
-        <v>6518</v>
+        <v>3048</v>
       </c>
       <c r="M213" s="5">
-        <v>1926</v>
+        <v>1743</v>
       </c>
       <c r="N213" s="5">
-        <v>1633</v>
+        <v>958</v>
       </c>
       <c r="O213" s="5">
-        <v>3177</v>
+        <v>1888</v>
       </c>
       <c r="P213" s="5">
-        <v>1503</v>
+        <v>838</v>
       </c>
       <c r="Q213" s="5">
-        <v>3195</v>
+        <v>1371</v>
       </c>
       <c r="R213" s="5">
-        <v>2368</v>
+        <v>1134</v>
       </c>
       <c r="S213" s="5">
-        <v>3674</v>
+        <v>2004</v>
       </c>
       <c r="T213" s="5">
-        <v>3174</v>
+        <v>2199</v>
       </c>
       <c r="U213" s="5">
-        <v>4995</v>
+        <v>2347</v>
       </c>
       <c r="V213" s="5"/>
       <c r="W213" s="5"/>
@@ -16385,158 +16365,148 @@
       <c r="Z213" s="5"/>
     </row>
     <row r="214" spans="1:40">
-      <c r="A214" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="B214" s="5"/>
-      <c r="C214" s="5"/>
-      <c r="D214" s="5"/>
-      <c r="E214" s="5"/>
-      <c r="F214" s="5"/>
-      <c r="G214" s="5"/>
-      <c r="H214" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="I214" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J214" s="6"/>
+      <c r="A214" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="B214" s="27">
+        <v>753355</v>
+      </c>
+      <c r="C214" s="27">
+        <v>53625</v>
+      </c>
+      <c r="D214" s="27">
+        <v>34085</v>
+      </c>
+      <c r="E214" s="27">
+        <v>40690</v>
+      </c>
+      <c r="F214" s="27">
+        <v>3140</v>
+      </c>
+      <c r="G214" s="27">
+        <v>2286</v>
+      </c>
+      <c r="H214" s="28">
+        <v>71.2</v>
+      </c>
+      <c r="I214" s="28">
+        <v>43.8</v>
+      </c>
+      <c r="J214" s="28"/>
       <c r="K214" s="5"/>
-      <c r="L214" s="5">
-        <v>3048</v>
-      </c>
-      <c r="M214" s="5">
-        <v>1743</v>
-      </c>
-      <c r="N214" s="5">
-        <v>958</v>
-      </c>
-      <c r="O214" s="5">
-        <v>1888</v>
-      </c>
-      <c r="P214" s="5">
-        <v>838</v>
-      </c>
-      <c r="Q214" s="5">
-        <v>1371</v>
-      </c>
-      <c r="R214" s="5">
-        <v>1134</v>
-      </c>
-      <c r="S214" s="5">
-        <v>2004</v>
-      </c>
-      <c r="T214" s="5">
-        <v>2199</v>
-      </c>
-      <c r="U214" s="5">
-        <v>2347</v>
-      </c>
-      <c r="V214" s="5"/>
-      <c r="W214" s="5"/>
-      <c r="X214" s="5"/>
-      <c r="Y214" s="5"/>
-      <c r="Z214" s="5"/>
+      <c r="L214" s="27">
+        <v>149120</v>
+      </c>
+      <c r="M214" s="27">
+        <v>154257</v>
+      </c>
+      <c r="N214" s="27">
+        <v>185340</v>
+      </c>
+      <c r="O214" s="27">
+        <v>215726</v>
+      </c>
+      <c r="P214" s="27">
+        <v>48912</v>
+      </c>
+      <c r="Q214" s="27"/>
+      <c r="R214" s="27"/>
+      <c r="S214" s="27"/>
+      <c r="T214" s="27"/>
+      <c r="U214" s="27"/>
+      <c r="V214" s="27"/>
+      <c r="W214" s="27"/>
+      <c r="X214" s="27"/>
+      <c r="Y214" s="27"/>
+      <c r="Z214" s="27"/>
+      <c r="AB214" s="37">
+        <f>SUM(L214:Z214)</f>
+        <v>753355</v>
+      </c>
+      <c r="AC214" s="37">
+        <f>SUM(L215:Z215)</f>
+        <v>53625</v>
+      </c>
+      <c r="AD214" s="37">
+        <f>SUM(L216:Z216)</f>
+        <v>34085</v>
+      </c>
+      <c r="AF214" s="37">
+        <f>AB214-B214</f>
+        <v>0</v>
+      </c>
+      <c r="AG214" s="37">
+        <f>AC214-C214</f>
+        <v>0</v>
+      </c>
+      <c r="AH214" s="37">
+        <f>AD214-D214</f>
+        <v>0</v>
+      </c>
+      <c r="AJ214" s="38">
+        <f>C214/B214*1000</f>
+        <v>71.181581060721697</v>
+      </c>
+      <c r="AK214" s="38">
+        <f>D214/B214*1000</f>
+        <v>45.244273947873175</v>
+      </c>
+      <c r="AM214" s="38">
+        <f>AJ214-H214</f>
+        <v>-1.8418939278305402E-2</v>
+      </c>
+      <c r="AN214" s="38">
+        <f>AK214-I214</f>
+        <v>1.4442739478731781</v>
+      </c>
     </row>
     <row r="215" spans="1:40">
-      <c r="A215" s="26" t="s">
-        <v>215</v>
-      </c>
-      <c r="B215" s="27">
-        <v>753355</v>
-      </c>
-      <c r="C215" s="27">
-        <v>53625</v>
-      </c>
-      <c r="D215" s="27">
-        <v>34085</v>
-      </c>
-      <c r="E215" s="27">
-        <v>40690</v>
-      </c>
-      <c r="F215" s="27">
-        <v>3140</v>
-      </c>
-      <c r="G215" s="27">
-        <v>2286</v>
-      </c>
-      <c r="H215" s="28">
-        <v>71.2</v>
-      </c>
-      <c r="I215" s="28">
-        <v>43.8</v>
-      </c>
-      <c r="J215" s="28"/>
+      <c r="A215" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B215" s="5"/>
+      <c r="C215" s="5"/>
+      <c r="D215" s="5"/>
+      <c r="E215" s="5"/>
+      <c r="F215" s="5"/>
+      <c r="G215" s="5"/>
+      <c r="H215" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I215" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J215" s="6"/>
       <c r="K215" s="5"/>
-      <c r="L215" s="27">
-        <v>149120</v>
-      </c>
-      <c r="M215" s="27">
-        <v>154257</v>
-      </c>
-      <c r="N215" s="27">
-        <v>185340</v>
-      </c>
-      <c r="O215" s="27">
-        <v>215726</v>
-      </c>
-      <c r="P215" s="27">
-        <v>48912</v>
-      </c>
-      <c r="Q215" s="27"/>
-      <c r="R215" s="27"/>
-      <c r="S215" s="27"/>
-      <c r="T215" s="27"/>
-      <c r="U215" s="27"/>
-      <c r="V215" s="27"/>
-      <c r="W215" s="27"/>
-      <c r="X215" s="27"/>
-      <c r="Y215" s="27"/>
-      <c r="Z215" s="27"/>
-      <c r="AB215" s="37">
-        <f>SUM(L215:Z215)</f>
-        <v>753355</v>
-      </c>
-      <c r="AC215" s="37">
-        <f>SUM(L216:Z216)</f>
-        <v>53625</v>
-      </c>
-      <c r="AD215" s="37">
-        <f>SUM(L217:Z217)</f>
-        <v>34085</v>
-      </c>
-      <c r="AF215" s="37">
-        <f>AB215-B215</f>
-        <v>0</v>
-      </c>
-      <c r="AG215" s="37">
-        <f>AC215-C215</f>
-        <v>0</v>
-      </c>
-      <c r="AH215" s="37">
-        <f>AD215-D215</f>
-        <v>0</v>
-      </c>
-      <c r="AJ215" s="38">
-        <f>C215/B215*1000</f>
-        <v>71.181581060721697</v>
-      </c>
-      <c r="AK215" s="38">
-        <f>D215/B215*1000</f>
-        <v>45.244273947873175</v>
-      </c>
-      <c r="AM215" s="38">
-        <f>AJ215-H215</f>
-        <v>-1.8418939278305402E-2</v>
-      </c>
-      <c r="AN215" s="38">
-        <f>AK215-I215</f>
-        <v>1.4442739478731781</v>
-      </c>
+      <c r="L215" s="5">
+        <v>10891</v>
+      </c>
+      <c r="M215" s="5">
+        <v>10346</v>
+      </c>
+      <c r="N215" s="5">
+        <v>15815</v>
+      </c>
+      <c r="O215" s="5">
+        <v>15407</v>
+      </c>
+      <c r="P215" s="5">
+        <v>1166</v>
+      </c>
+      <c r="Q215" s="5"/>
+      <c r="R215" s="5"/>
+      <c r="S215" s="5"/>
+      <c r="T215" s="5"/>
+      <c r="U215" s="5"/>
+      <c r="V215" s="5"/>
+      <c r="W215" s="5"/>
+      <c r="X215" s="5"/>
+      <c r="Y215" s="5"/>
+      <c r="Z215" s="5"/>
     </row>
     <row r="216" spans="1:40">
       <c r="A216" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B216" s="5"/>
       <c r="C216" s="5"/>
@@ -16553,19 +16523,19 @@
       <c r="J216" s="6"/>
       <c r="K216" s="5"/>
       <c r="L216" s="5">
-        <v>10891</v>
+        <v>7158</v>
       </c>
       <c r="M216" s="5">
-        <v>10346</v>
+        <v>6612</v>
       </c>
       <c r="N216" s="5">
-        <v>15815</v>
+        <v>10301</v>
       </c>
       <c r="O216" s="5">
-        <v>15407</v>
+        <v>9160</v>
       </c>
       <c r="P216" s="5">
-        <v>1166</v>
+        <v>854</v>
       </c>
       <c r="Q216" s="5"/>
       <c r="R216" s="5"/>
@@ -16579,152 +16549,156 @@
       <c r="Z216" s="5"/>
     </row>
     <row r="217" spans="1:40">
-      <c r="A217" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B217" s="5"/>
-      <c r="C217" s="5"/>
-      <c r="D217" s="5"/>
-      <c r="E217" s="5"/>
-      <c r="F217" s="5"/>
-      <c r="G217" s="5"/>
-      <c r="H217" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="I217" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J217" s="6"/>
+      <c r="A217" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="B217" s="27">
+        <v>845083</v>
+      </c>
+      <c r="C217" s="27">
+        <v>30200</v>
+      </c>
+      <c r="D217" s="27">
+        <v>18409</v>
+      </c>
+      <c r="E217" s="27">
+        <v>106491</v>
+      </c>
+      <c r="F217" s="27">
+        <v>4175</v>
+      </c>
+      <c r="G217" s="27">
+        <v>2617</v>
+      </c>
+      <c r="H217" s="28">
+        <v>36.1</v>
+      </c>
+      <c r="I217" s="28">
+        <v>22</v>
+      </c>
+      <c r="J217" s="28"/>
       <c r="K217" s="5"/>
-      <c r="L217" s="5">
-        <v>7158</v>
-      </c>
-      <c r="M217" s="5">
-        <v>6612</v>
-      </c>
-      <c r="N217" s="5">
-        <v>10301</v>
-      </c>
-      <c r="O217" s="5">
-        <v>9160</v>
-      </c>
-      <c r="P217" s="5">
-        <v>854</v>
-      </c>
-      <c r="Q217" s="5"/>
-      <c r="R217" s="5"/>
-      <c r="S217" s="5"/>
-      <c r="T217" s="5"/>
-      <c r="U217" s="5"/>
-      <c r="V217" s="5"/>
-      <c r="W217" s="5"/>
-      <c r="X217" s="5"/>
-      <c r="Y217" s="5"/>
-      <c r="Z217" s="5"/>
+      <c r="L217" s="27">
+        <v>134098</v>
+      </c>
+      <c r="M217" s="27">
+        <v>197892</v>
+      </c>
+      <c r="N217" s="27">
+        <v>86838</v>
+      </c>
+      <c r="O217" s="27">
+        <v>113364</v>
+      </c>
+      <c r="P217" s="27">
+        <v>130450</v>
+      </c>
+      <c r="Q217" s="27">
+        <v>109707</v>
+      </c>
+      <c r="R217" s="27">
+        <v>72734</v>
+      </c>
+      <c r="S217" s="27"/>
+      <c r="T217" s="27"/>
+      <c r="U217" s="27"/>
+      <c r="V217" s="27"/>
+      <c r="W217" s="27"/>
+      <c r="X217" s="27"/>
+      <c r="Y217" s="27"/>
+      <c r="Z217" s="27"/>
+      <c r="AB217" s="37">
+        <f>SUM(L217:Z217)</f>
+        <v>845083</v>
+      </c>
+      <c r="AC217" s="37">
+        <f>SUM(L218:Z218)</f>
+        <v>30200</v>
+      </c>
+      <c r="AD217" s="37">
+        <f>SUM(L219:Z219)</f>
+        <v>18409</v>
+      </c>
+      <c r="AF217" s="37">
+        <f>AB217-B217</f>
+        <v>0</v>
+      </c>
+      <c r="AG217" s="37">
+        <f>AC217-C217</f>
+        <v>0</v>
+      </c>
+      <c r="AH217" s="37">
+        <f>AD217-D217</f>
+        <v>0</v>
+      </c>
+      <c r="AJ217" s="38">
+        <f>C217/B217*1000</f>
+        <v>35.736134793860487</v>
+      </c>
+      <c r="AK217" s="38">
+        <f>D217/B217*1000</f>
+        <v>21.78365911987343</v>
+      </c>
+      <c r="AM217" s="38">
+        <f>AJ217-H217</f>
+        <v>-0.3638652061395149</v>
+      </c>
+      <c r="AN217" s="38">
+        <f>AK217-I217</f>
+        <v>-0.2163408801265696</v>
+      </c>
     </row>
     <row r="218" spans="1:40">
-      <c r="A218" s="26" t="s">
-        <v>218</v>
-      </c>
-      <c r="B218" s="27">
-        <v>845083</v>
-      </c>
-      <c r="C218" s="27">
-        <v>30200</v>
-      </c>
-      <c r="D218" s="27">
-        <v>18409</v>
-      </c>
-      <c r="E218" s="27">
-        <v>106491</v>
-      </c>
-      <c r="F218" s="27">
-        <v>4175</v>
-      </c>
-      <c r="G218" s="27">
-        <v>2617</v>
-      </c>
-      <c r="H218" s="28">
-        <v>36.1</v>
-      </c>
-      <c r="I218" s="28">
-        <v>22</v>
-      </c>
-      <c r="J218" s="28"/>
+      <c r="A218" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B218" s="5"/>
+      <c r="C218" s="5"/>
+      <c r="D218" s="5"/>
+      <c r="E218" s="5"/>
+      <c r="F218" s="5"/>
+      <c r="G218" s="5"/>
+      <c r="H218" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I218" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J218" s="6"/>
       <c r="K218" s="5"/>
-      <c r="L218" s="27">
-        <v>134098</v>
-      </c>
-      <c r="M218" s="27">
-        <v>197892</v>
-      </c>
-      <c r="N218" s="27">
-        <v>86838</v>
-      </c>
-      <c r="O218" s="27">
-        <v>113364</v>
-      </c>
-      <c r="P218" s="27">
-        <v>130450</v>
-      </c>
-      <c r="Q218" s="27">
-        <v>109707</v>
-      </c>
-      <c r="R218" s="27">
-        <v>72734</v>
-      </c>
-      <c r="S218" s="27"/>
-      <c r="T218" s="27"/>
-      <c r="U218" s="27"/>
-      <c r="V218" s="27"/>
-      <c r="W218" s="27"/>
-      <c r="X218" s="27"/>
-      <c r="Y218" s="27"/>
-      <c r="Z218" s="27"/>
-      <c r="AB218" s="37">
-        <f>SUM(L218:Z218)</f>
-        <v>845083</v>
-      </c>
-      <c r="AC218" s="37">
-        <f>SUM(L219:Z219)</f>
-        <v>30200</v>
-      </c>
-      <c r="AD218" s="37">
-        <f>SUM(L220:Z220)</f>
-        <v>18409</v>
-      </c>
-      <c r="AF218" s="37">
-        <f>AB218-B218</f>
-        <v>0</v>
-      </c>
-      <c r="AG218" s="37">
-        <f>AC218-C218</f>
-        <v>0</v>
-      </c>
-      <c r="AH218" s="37">
-        <f>AD218-D218</f>
-        <v>0</v>
-      </c>
-      <c r="AJ218" s="38">
-        <f>C218/B218*1000</f>
-        <v>35.736134793860487</v>
-      </c>
-      <c r="AK218" s="38">
-        <f>D218/B218*1000</f>
-        <v>21.78365911987343</v>
-      </c>
-      <c r="AM218" s="38">
-        <f>AJ218-H218</f>
-        <v>-0.3638652061395149</v>
-      </c>
-      <c r="AN218" s="38">
-        <f>AK218-I218</f>
-        <v>-0.2163408801265696</v>
-      </c>
+      <c r="L218" s="5">
+        <v>4566</v>
+      </c>
+      <c r="M218" s="5">
+        <v>4080</v>
+      </c>
+      <c r="N218" s="5">
+        <v>3726</v>
+      </c>
+      <c r="O218" s="5">
+        <v>3301</v>
+      </c>
+      <c r="P218" s="5">
+        <v>7868</v>
+      </c>
+      <c r="Q218" s="5">
+        <v>4147</v>
+      </c>
+      <c r="R218" s="5">
+        <v>2512</v>
+      </c>
+      <c r="S218" s="5"/>
+      <c r="T218" s="5"/>
+      <c r="U218" s="5"/>
+      <c r="V218" s="5"/>
+      <c r="W218" s="5"/>
+      <c r="X218" s="5"/>
+      <c r="Y218" s="5"/>
+      <c r="Z218" s="5"/>
     </row>
     <row r="219" spans="1:40">
       <c r="A219" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
@@ -16741,25 +16715,25 @@
       <c r="J219" s="6"/>
       <c r="K219" s="5"/>
       <c r="L219" s="5">
-        <v>4566</v>
+        <v>2336</v>
       </c>
       <c r="M219" s="5">
-        <v>4080</v>
+        <v>2937</v>
       </c>
       <c r="N219" s="5">
-        <v>3726</v>
+        <v>2209</v>
       </c>
       <c r="O219" s="5">
-        <v>3301</v>
+        <v>1598</v>
       </c>
       <c r="P219" s="5">
-        <v>7868</v>
+        <v>5092</v>
       </c>
       <c r="Q219" s="5">
-        <v>4147</v>
+        <v>2566</v>
       </c>
       <c r="R219" s="5">
-        <v>2512</v>
+        <v>1671</v>
       </c>
       <c r="S219" s="5"/>
       <c r="T219" s="5"/>
@@ -16771,160 +16745,164 @@
       <c r="Z219" s="5"/>
     </row>
     <row r="220" spans="1:40">
-      <c r="A220" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="B220" s="5"/>
-      <c r="C220" s="5"/>
-      <c r="D220" s="5"/>
-      <c r="E220" s="5"/>
-      <c r="F220" s="5"/>
-      <c r="G220" s="5"/>
-      <c r="H220" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="I220" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J220" s="6"/>
+      <c r="A220" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="B220" s="27">
+        <v>986247</v>
+      </c>
+      <c r="C220" s="27">
+        <v>32288</v>
+      </c>
+      <c r="D220" s="27">
+        <v>20396</v>
+      </c>
+      <c r="E220" s="27">
+        <v>162351</v>
+      </c>
+      <c r="F220" s="27">
+        <v>4122</v>
+      </c>
+      <c r="G220" s="27">
+        <v>3102</v>
+      </c>
+      <c r="H220" s="28">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="I220" s="28">
+        <v>20.7</v>
+      </c>
+      <c r="J220" s="28"/>
       <c r="K220" s="5"/>
-      <c r="L220" s="5">
-        <v>2336</v>
-      </c>
-      <c r="M220" s="5">
-        <v>2937</v>
-      </c>
-      <c r="N220" s="5">
-        <v>2209</v>
-      </c>
-      <c r="O220" s="5">
-        <v>1598</v>
-      </c>
-      <c r="P220" s="5">
-        <v>5092</v>
-      </c>
-      <c r="Q220" s="5">
-        <v>2566</v>
-      </c>
-      <c r="R220" s="5">
-        <v>1671</v>
-      </c>
-      <c r="S220" s="5"/>
-      <c r="T220" s="5"/>
-      <c r="U220" s="5"/>
-      <c r="V220" s="5"/>
-      <c r="W220" s="5"/>
-      <c r="X220" s="5"/>
-      <c r="Y220" s="5"/>
-      <c r="Z220" s="5"/>
+      <c r="L220" s="27">
+        <v>252072</v>
+      </c>
+      <c r="M220" s="27">
+        <v>68958</v>
+      </c>
+      <c r="N220" s="27">
+        <v>65183</v>
+      </c>
+      <c r="O220" s="27">
+        <v>135766</v>
+      </c>
+      <c r="P220" s="27">
+        <v>174987</v>
+      </c>
+      <c r="Q220" s="27">
+        <v>74988</v>
+      </c>
+      <c r="R220" s="27">
+        <v>107095</v>
+      </c>
+      <c r="S220" s="27">
+        <v>71564</v>
+      </c>
+      <c r="T220" s="27">
+        <v>35634</v>
+      </c>
+      <c r="U220" s="27"/>
+      <c r="V220" s="27"/>
+      <c r="W220" s="27"/>
+      <c r="X220" s="27"/>
+      <c r="Y220" s="27"/>
+      <c r="Z220" s="27"/>
+      <c r="AB220" s="37">
+        <f>SUM(L220:Z220)</f>
+        <v>986247</v>
+      </c>
+      <c r="AC220" s="37">
+        <f>SUM(L221:Z221)</f>
+        <v>32288</v>
+      </c>
+      <c r="AD220" s="37">
+        <f>SUM(L222:Z222)</f>
+        <v>20396</v>
+      </c>
+      <c r="AF220" s="37">
+        <f>AB220-B220</f>
+        <v>0</v>
+      </c>
+      <c r="AG220" s="37">
+        <f>AC220-C220</f>
+        <v>0</v>
+      </c>
+      <c r="AH220" s="37">
+        <f>AD220-D220</f>
+        <v>0</v>
+      </c>
+      <c r="AJ220" s="38">
+        <f>C220/B220*1000</f>
+        <v>32.738249140428309</v>
+      </c>
+      <c r="AK220" s="38">
+        <f>D220/B220*1000</f>
+        <v>20.680417785808221</v>
+      </c>
+      <c r="AM220" s="38">
+        <f>AJ220-H220</f>
+        <v>3.824914042830585E-2</v>
+      </c>
+      <c r="AN220" s="38">
+        <f>AK220-I220</f>
+        <v>-1.9582214191778746E-2</v>
+      </c>
     </row>
     <row r="221" spans="1:40">
-      <c r="A221" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="B221" s="27">
-        <v>986247</v>
-      </c>
-      <c r="C221" s="27">
-        <v>32288</v>
-      </c>
-      <c r="D221" s="27">
-        <v>20396</v>
-      </c>
-      <c r="E221" s="27">
-        <v>162351</v>
-      </c>
-      <c r="F221" s="27">
-        <v>4122</v>
-      </c>
-      <c r="G221" s="27">
-        <v>3102</v>
-      </c>
-      <c r="H221" s="28">
-        <v>32.700000000000003</v>
-      </c>
-      <c r="I221" s="28">
-        <v>20.7</v>
-      </c>
-      <c r="J221" s="28"/>
+      <c r="A221" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B221" s="5"/>
+      <c r="C221" s="5"/>
+      <c r="D221" s="5"/>
+      <c r="E221" s="5"/>
+      <c r="F221" s="5"/>
+      <c r="G221" s="5"/>
+      <c r="H221" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I221" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J221" s="6"/>
       <c r="K221" s="5"/>
-      <c r="L221" s="27">
-        <v>252072</v>
-      </c>
-      <c r="M221" s="27">
-        <v>68958</v>
-      </c>
-      <c r="N221" s="27">
-        <v>65183</v>
-      </c>
-      <c r="O221" s="27">
-        <v>135766</v>
-      </c>
-      <c r="P221" s="27">
-        <v>174987</v>
-      </c>
-      <c r="Q221" s="27">
-        <v>74988</v>
-      </c>
-      <c r="R221" s="27">
-        <v>107095</v>
-      </c>
-      <c r="S221" s="27">
-        <v>71564</v>
-      </c>
-      <c r="T221" s="27">
-        <v>35634</v>
-      </c>
-      <c r="U221" s="27"/>
-      <c r="V221" s="27"/>
-      <c r="W221" s="27"/>
-      <c r="X221" s="27"/>
-      <c r="Y221" s="27"/>
-      <c r="Z221" s="27"/>
-      <c r="AB221" s="37">
-        <f>SUM(L221:Z221)</f>
-        <v>986247</v>
-      </c>
-      <c r="AC221" s="37">
-        <f>SUM(L222:Z222)</f>
-        <v>32288</v>
-      </c>
-      <c r="AD221" s="37">
-        <f>SUM(L223:Z223)</f>
-        <v>20396</v>
-      </c>
-      <c r="AF221" s="37">
-        <f>AB221-B221</f>
-        <v>0</v>
-      </c>
-      <c r="AG221" s="37">
-        <f>AC221-C221</f>
-        <v>0</v>
-      </c>
-      <c r="AH221" s="37">
-        <f>AD221-D221</f>
-        <v>0</v>
-      </c>
-      <c r="AJ221" s="38">
-        <f>C221/B221*1000</f>
-        <v>32.738249140428309</v>
-      </c>
-      <c r="AK221" s="38">
-        <f>D221/B221*1000</f>
-        <v>20.680417785808221</v>
-      </c>
-      <c r="AM221" s="38">
-        <f>AJ221-H221</f>
-        <v>3.824914042830585E-2</v>
-      </c>
-      <c r="AN221" s="38">
-        <f>AK221-I221</f>
-        <v>-1.9582214191778746E-2</v>
-      </c>
+      <c r="L221" s="5">
+        <v>5761</v>
+      </c>
+      <c r="M221" s="5">
+        <v>3135</v>
+      </c>
+      <c r="N221" s="5">
+        <v>2333</v>
+      </c>
+      <c r="O221" s="5">
+        <v>3857</v>
+      </c>
+      <c r="P221" s="5">
+        <v>7003</v>
+      </c>
+      <c r="Q221" s="5">
+        <v>2621</v>
+      </c>
+      <c r="R221" s="5">
+        <v>3901</v>
+      </c>
+      <c r="S221" s="5">
+        <v>2599</v>
+      </c>
+      <c r="T221" s="5">
+        <v>1078</v>
+      </c>
+      <c r="U221" s="5"/>
+      <c r="V221" s="5"/>
+      <c r="W221" s="5"/>
+      <c r="X221" s="5"/>
+      <c r="Y221" s="5"/>
+      <c r="Z221" s="5"/>
     </row>
     <row r="222" spans="1:40">
       <c r="A222" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B222" s="5"/>
       <c r="C222" s="5"/>
@@ -16941,31 +16919,31 @@
       <c r="J222" s="6"/>
       <c r="K222" s="5"/>
       <c r="L222" s="5">
-        <v>5761</v>
+        <v>4096</v>
       </c>
       <c r="M222" s="5">
-        <v>3135</v>
+        <v>1982</v>
       </c>
       <c r="N222" s="5">
-        <v>2333</v>
+        <v>1209</v>
       </c>
       <c r="O222" s="5">
-        <v>3857</v>
+        <v>2191</v>
       </c>
       <c r="P222" s="5">
-        <v>7003</v>
+        <v>3900</v>
       </c>
       <c r="Q222" s="5">
-        <v>2621</v>
+        <v>1582</v>
       </c>
       <c r="R222" s="5">
-        <v>3901</v>
+        <v>2757</v>
       </c>
       <c r="S222" s="5">
-        <v>2599</v>
+        <v>1716</v>
       </c>
       <c r="T222" s="5">
-        <v>1078</v>
+        <v>963</v>
       </c>
       <c r="U222" s="5"/>
       <c r="V222" s="5"/>
@@ -16975,160 +16953,156 @@
       <c r="Z222" s="5"/>
     </row>
     <row r="223" spans="1:40">
-      <c r="A223" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="B223" s="5"/>
-      <c r="C223" s="5"/>
-      <c r="D223" s="5"/>
-      <c r="E223" s="5"/>
-      <c r="F223" s="5"/>
-      <c r="G223" s="5"/>
-      <c r="H223" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="I223" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J223" s="6"/>
+      <c r="A223" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="B223" s="27">
+        <v>741690</v>
+      </c>
+      <c r="C223" s="27">
+        <v>29619</v>
+      </c>
+      <c r="D223" s="27">
+        <v>16257</v>
+      </c>
+      <c r="E223" s="27">
+        <v>61048</v>
+      </c>
+      <c r="F223" s="27">
+        <v>3578</v>
+      </c>
+      <c r="G223" s="27">
+        <v>2149</v>
+      </c>
+      <c r="H223" s="28">
+        <v>35.1</v>
+      </c>
+      <c r="I223" s="28">
+        <v>19</v>
+      </c>
+      <c r="J223" s="28"/>
       <c r="K223" s="5"/>
-      <c r="L223" s="5">
-        <v>4096</v>
-      </c>
-      <c r="M223" s="5">
-        <v>1982</v>
-      </c>
-      <c r="N223" s="5">
-        <v>1209</v>
-      </c>
-      <c r="O223" s="5">
-        <v>2191</v>
-      </c>
-      <c r="P223" s="5">
-        <v>3900</v>
-      </c>
-      <c r="Q223" s="5">
-        <v>1582</v>
-      </c>
-      <c r="R223" s="5">
-        <v>2757</v>
-      </c>
-      <c r="S223" s="5">
-        <v>1716</v>
-      </c>
-      <c r="T223" s="5">
-        <v>963</v>
-      </c>
-      <c r="U223" s="5"/>
-      <c r="V223" s="5"/>
-      <c r="W223" s="5"/>
-      <c r="X223" s="5"/>
-      <c r="Y223" s="5"/>
-      <c r="Z223" s="5"/>
+      <c r="L223" s="27">
+        <v>118951</v>
+      </c>
+      <c r="M223" s="27">
+        <v>155415</v>
+      </c>
+      <c r="N223" s="27">
+        <v>95137</v>
+      </c>
+      <c r="O223" s="27">
+        <v>120123</v>
+      </c>
+      <c r="P223" s="27">
+        <v>68253</v>
+      </c>
+      <c r="Q223" s="27">
+        <v>79023</v>
+      </c>
+      <c r="R223" s="27">
+        <v>104788</v>
+      </c>
+      <c r="S223" s="27"/>
+      <c r="T223" s="27"/>
+      <c r="U223" s="27"/>
+      <c r="V223" s="27"/>
+      <c r="W223" s="27"/>
+      <c r="X223" s="27"/>
+      <c r="Y223" s="27"/>
+      <c r="Z223" s="27"/>
+      <c r="AB223" s="37">
+        <f>SUM(L223:Z223)</f>
+        <v>741690</v>
+      </c>
+      <c r="AC223" s="37">
+        <f>SUM(L224:Z224)</f>
+        <v>29619</v>
+      </c>
+      <c r="AD223" s="37">
+        <f>SUM(L225:Z225)</f>
+        <v>16257</v>
+      </c>
+      <c r="AF223" s="37">
+        <f>AB223-B223</f>
+        <v>0</v>
+      </c>
+      <c r="AG223" s="37">
+        <f>AC223-C223</f>
+        <v>0</v>
+      </c>
+      <c r="AH223" s="37">
+        <f>AD223-D223</f>
+        <v>0</v>
+      </c>
+      <c r="AJ223" s="38">
+        <f>C223/B223*1000</f>
+        <v>39.934473971605385</v>
+      </c>
+      <c r="AK223" s="38">
+        <f>D223/B223*1000</f>
+        <v>21.918860979654571</v>
+      </c>
+      <c r="AM223" s="38">
+        <f>AJ223-H223</f>
+        <v>4.8344739716053837</v>
+      </c>
+      <c r="AN223" s="38">
+        <f>AK223-I223</f>
+        <v>2.9188609796545713</v>
+      </c>
     </row>
     <row r="224" spans="1:40">
-      <c r="A224" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="B224" s="27">
-        <v>741690</v>
-      </c>
-      <c r="C224" s="27">
-        <v>29619</v>
-      </c>
-      <c r="D224" s="27">
-        <v>16257</v>
-      </c>
-      <c r="E224" s="27">
-        <v>61048</v>
-      </c>
-      <c r="F224" s="27">
-        <v>3578</v>
-      </c>
-      <c r="G224" s="27">
-        <v>2149</v>
-      </c>
-      <c r="H224" s="28">
-        <v>35.1</v>
-      </c>
-      <c r="I224" s="28">
-        <v>19</v>
-      </c>
-      <c r="J224" s="28"/>
+      <c r="A224" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B224" s="5"/>
+      <c r="C224" s="5"/>
+      <c r="D224" s="5"/>
+      <c r="E224" s="5"/>
+      <c r="F224" s="5"/>
+      <c r="G224" s="5"/>
+      <c r="H224" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I224" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J224" s="6"/>
       <c r="K224" s="5"/>
-      <c r="L224" s="27">
-        <v>118951</v>
-      </c>
-      <c r="M224" s="27">
-        <v>155415</v>
-      </c>
-      <c r="N224" s="27">
-        <v>95137</v>
-      </c>
-      <c r="O224" s="27">
-        <v>120123</v>
-      </c>
-      <c r="P224" s="27">
-        <v>68253</v>
-      </c>
-      <c r="Q224" s="27">
-        <v>79023</v>
-      </c>
-      <c r="R224" s="27">
-        <v>104788</v>
-      </c>
-      <c r="S224" s="27"/>
-      <c r="T224" s="27"/>
-      <c r="U224" s="27"/>
-      <c r="V224" s="27"/>
-      <c r="W224" s="27"/>
-      <c r="X224" s="27"/>
-      <c r="Y224" s="27"/>
-      <c r="Z224" s="27"/>
-      <c r="AB224" s="37">
-        <f>SUM(L224:Z224)</f>
-        <v>741690</v>
-      </c>
-      <c r="AC224" s="37">
-        <f>SUM(L225:Z225)</f>
-        <v>29619</v>
-      </c>
-      <c r="AD224" s="37">
-        <f>SUM(L226:Z226)</f>
-        <v>16257</v>
-      </c>
-      <c r="AF224" s="37">
-        <f>AB224-B224</f>
-        <v>0</v>
-      </c>
-      <c r="AG224" s="37">
-        <f>AC224-C224</f>
-        <v>0</v>
-      </c>
-      <c r="AH224" s="37">
-        <f>AD224-D224</f>
-        <v>0</v>
-      </c>
-      <c r="AJ224" s="38">
-        <f>C224/B224*1000</f>
-        <v>39.934473971605385</v>
-      </c>
-      <c r="AK224" s="38">
-        <f>D224/B224*1000</f>
-        <v>21.918860979654571</v>
-      </c>
-      <c r="AM224" s="38">
-        <f>AJ224-H224</f>
-        <v>4.8344739716053837</v>
-      </c>
-      <c r="AN224" s="38">
-        <f>AK224-I224</f>
-        <v>2.9188609796545713</v>
-      </c>
+      <c r="L224" s="5">
+        <v>4078</v>
+      </c>
+      <c r="M224" s="5">
+        <v>6141</v>
+      </c>
+      <c r="N224" s="5">
+        <v>4767</v>
+      </c>
+      <c r="O224" s="5">
+        <v>5584</v>
+      </c>
+      <c r="P224" s="5">
+        <v>1318</v>
+      </c>
+      <c r="Q224" s="5">
+        <v>2881</v>
+      </c>
+      <c r="R224" s="5">
+        <v>4850</v>
+      </c>
+      <c r="S224" s="5"/>
+      <c r="T224" s="5"/>
+      <c r="U224" s="5"/>
+      <c r="V224" s="5"/>
+      <c r="W224" s="5"/>
+      <c r="X224" s="5"/>
+      <c r="Y224" s="5"/>
+      <c r="Z224" s="5"/>
     </row>
     <row r="225" spans="1:40">
       <c r="A225" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B225" s="5"/>
       <c r="C225" s="5"/>
@@ -17145,25 +17119,25 @@
       <c r="J225" s="6"/>
       <c r="K225" s="5"/>
       <c r="L225" s="5">
-        <v>4078</v>
+        <v>3058</v>
       </c>
       <c r="M225" s="5">
-        <v>6141</v>
+        <v>3524</v>
       </c>
       <c r="N225" s="5">
-        <v>4767</v>
+        <v>2453</v>
       </c>
       <c r="O225" s="5">
-        <v>5584</v>
+        <v>1972</v>
       </c>
       <c r="P225" s="5">
-        <v>1318</v>
+        <v>577</v>
       </c>
       <c r="Q225" s="5">
-        <v>2881</v>
+        <v>1537</v>
       </c>
       <c r="R225" s="5">
-        <v>4850</v>
+        <v>3136</v>
       </c>
       <c r="S225" s="5"/>
       <c r="T225" s="5"/>
@@ -17175,52 +17149,77 @@
       <c r="Z225" s="5"/>
     </row>
     <row r="226" spans="1:40">
-      <c r="A226" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="B226" s="5"/>
-      <c r="C226" s="5"/>
-      <c r="D226" s="5"/>
-      <c r="E226" s="5"/>
-      <c r="F226" s="5"/>
-      <c r="G226" s="5"/>
-      <c r="H226" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="I226" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J226" s="6"/>
+      <c r="A226" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="B226" s="27">
+        <v>70892</v>
+      </c>
+      <c r="C226" s="27">
+        <v>3752</v>
+      </c>
+      <c r="D226" s="27">
+        <v>3320</v>
+      </c>
+      <c r="E226" s="27">
+        <v>2517</v>
+      </c>
+      <c r="F226" s="27">
+        <v>108</v>
+      </c>
+      <c r="G226" s="27">
+        <v>47</v>
+      </c>
+      <c r="H226" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="I226" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J226" s="28" t="s">
+        <v>221</v>
+      </c>
       <c r="K226" s="5"/>
-      <c r="L226" s="5">
-        <v>3058</v>
-      </c>
-      <c r="M226" s="5">
-        <v>3524</v>
-      </c>
-      <c r="N226" s="5">
-        <v>2453</v>
-      </c>
-      <c r="O226" s="5">
-        <v>1972</v>
-      </c>
-      <c r="P226" s="5">
-        <v>577</v>
-      </c>
-      <c r="Q226" s="5">
-        <v>1537</v>
-      </c>
-      <c r="R226" s="5">
-        <v>3136</v>
-      </c>
-      <c r="S226" s="5"/>
-      <c r="T226" s="5"/>
-      <c r="U226" s="5"/>
-      <c r="V226" s="5"/>
-      <c r="W226" s="5"/>
-      <c r="X226" s="5"/>
-      <c r="Y226" s="5"/>
-      <c r="Z226" s="5"/>
+      <c r="L226" s="27"/>
+      <c r="M226" s="27"/>
+      <c r="N226" s="27"/>
+      <c r="O226" s="27"/>
+      <c r="P226" s="27"/>
+      <c r="Q226" s="27"/>
+      <c r="R226" s="27"/>
+      <c r="S226" s="27"/>
+      <c r="T226" s="27"/>
+      <c r="U226" s="27"/>
+      <c r="V226" s="27"/>
+      <c r="W226" s="27"/>
+      <c r="X226" s="27"/>
+      <c r="Y226" s="27"/>
+      <c r="Z226" s="27"/>
+      <c r="AB226" s="37">
+        <f>B226</f>
+        <v>70892</v>
+      </c>
+      <c r="AC226" s="37">
+        <f>C226</f>
+        <v>3752</v>
+      </c>
+      <c r="AD226" s="37">
+        <f>D226</f>
+        <v>3320</v>
+      </c>
+      <c r="AF226" s="39"/>
+      <c r="AG226" s="39"/>
+      <c r="AH226" s="39"/>
+      <c r="AJ226" s="38">
+        <f>C226/B226*1000</f>
+        <v>52.925576933927665</v>
+      </c>
+      <c r="AK226" s="38">
+        <f>D226/B226*1000</f>
+        <v>46.831800485245161</v>
+      </c>
+      <c r="AM226" s="38"/>
+      <c r="AN226" s="38"/>
     </row>
     <row r="227" spans="1:40">
       <c r="A227" s="29" t="s">
@@ -17262,28 +17261,28 @@
       <c r="Y227" s="30"/>
       <c r="Z227" s="30"/>
       <c r="AB227" s="43">
-        <f>SUM(AB196:AB226)</f>
-        <v>8640283</v>
+        <f>SUM(AB196:AB225)</f>
+        <v>8569391</v>
       </c>
       <c r="AC227" s="43">
-        <f>SUM(AC196:AC226)</f>
-        <v>353824</v>
+        <f>SUM(AC196:AC225)</f>
+        <v>350072</v>
       </c>
       <c r="AD227" s="43">
-        <f>SUM(AD196:AD226)</f>
-        <v>225467</v>
+        <f>SUM(AD196:AD225)</f>
+        <v>222147</v>
       </c>
       <c r="AF227" s="43">
         <f>AB227-B227</f>
-        <v>40690</v>
+        <v>-30202</v>
       </c>
       <c r="AG227" s="43">
         <f>AC227-C227</f>
-        <v>6007</v>
+        <v>2255</v>
       </c>
       <c r="AH227" s="43">
         <f>AD227-D227</f>
-        <v>3705</v>
+        <v>385</v>
       </c>
       <c r="AJ227" s="44">
         <f>C227/B227*1000</f>
@@ -17294,11 +17293,11 @@
         <v>25.787499478172979</v>
       </c>
       <c r="AM227" s="44">
-        <f>AJ227-H227</f>
+        <f t="shared" ref="AM227:AN229" si="6">AJ227-H227</f>
         <v>-0.85424867200110555</v>
       </c>
       <c r="AN227" s="44">
-        <f>AK227-I227</f>
+        <f t="shared" si="6"/>
         <v>-0.31250052182702248</v>
       </c>
     </row>
@@ -17371,11 +17370,11 @@
         <v>25.542062048281625</v>
       </c>
       <c r="AM228" s="38">
-        <f>AJ228-H228</f>
+        <f t="shared" si="6"/>
         <v>-0.77149810708490918</v>
       </c>
       <c r="AN228" s="38">
-        <f>AK228-I228</f>
+        <f t="shared" si="6"/>
         <v>-0.45793795171837459</v>
       </c>
     </row>
@@ -17469,11 +17468,11 @@
         <v>41.179037786254661</v>
       </c>
       <c r="AM229" s="38">
-        <f>AJ229-H229</f>
+        <f t="shared" si="6"/>
         <v>-0.55861498485299421</v>
       </c>
       <c r="AN229" s="38">
-        <f>AK229-I229</f>
+        <f t="shared" si="6"/>
         <v>-0.42096221374534082</v>
       </c>
     </row>
@@ -18945,15 +18944,15 @@
         <v>163383</v>
       </c>
       <c r="AF253" s="43">
-        <f>AB253-B253</f>
+        <f t="shared" ref="AF253:AH254" si="7">AB253-B253</f>
         <v>-609748</v>
       </c>
       <c r="AG253" s="43">
-        <f>AC253-C253</f>
+        <f t="shared" si="7"/>
         <v>-24095</v>
       </c>
       <c r="AH253" s="43">
-        <f>AD253-D253</f>
+        <f t="shared" si="7"/>
         <v>-14501</v>
       </c>
       <c r="AJ253" s="44">
@@ -19041,15 +19040,15 @@
         <v>9979</v>
       </c>
       <c r="AF254" s="37">
-        <f>AB254-B254</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AG254" s="37">
-        <f>AC254-C254</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AH254" s="37">
-        <f>AD254-D254</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AJ254" s="38">
@@ -20627,15 +20626,15 @@
         <v>84855</v>
       </c>
       <c r="AF281" s="43">
-        <f>AB281-B281</f>
+        <f t="shared" ref="AF281:AH282" si="8">AB281-B281</f>
         <v>-684683</v>
       </c>
       <c r="AG281" s="43">
-        <f>AC281-C281</f>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="AH281" s="43">
-        <f>AD281-D281</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ281" s="44">
@@ -20696,27 +20695,27 @@
       <c r="Z282" s="41"/>
       <c r="AB282" s="45">
         <f>SUM(AB195, AB227, AB253, AB281)</f>
-        <v>123569478</v>
+        <v>123498586</v>
       </c>
       <c r="AC282" s="45">
         <f>SUM(AC195, AC227, AC253, AC281)</f>
-        <v>5636258</v>
+        <v>5632506</v>
       </c>
       <c r="AD282" s="45">
         <f>SUM(AD195, AD227, AD253, AD281)</f>
-        <v>3907126</v>
+        <v>3903806</v>
       </c>
       <c r="AF282" s="43">
-        <f>AB282-B282</f>
-        <v>-1229220</v>
+        <f t="shared" si="8"/>
+        <v>-1300112</v>
       </c>
       <c r="AG282" s="43">
-        <f>AC282-C282</f>
-        <v>-14805</v>
+        <f t="shared" si="8"/>
+        <v>-18557</v>
       </c>
       <c r="AH282" s="43">
-        <f>AD282-D282</f>
-        <v>37190</v>
+        <f t="shared" si="8"/>
+        <v>33870</v>
       </c>
       <c r="AJ282" s="44">
         <f>C282/B282*1000</f>
